--- a/VerveStacks_CHN_grids_syn_5/SuppXLS/Scen_Par-NGFS.xlsx
+++ b/VerveStacks_CHN_grids_syn_5/SuppXLS/Scen_Par-NGFS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\VerveStacks\assumptions\VerveStacks_ISO_template\SuppXLS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN_grids_syn_5\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AE794E3-D286-477D-8749-66F025C465CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62C28E02-5D3D-4893-9819-9D73D0C86F72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28898" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Veda" sheetId="1" r:id="rId1"/>
